--- a/49877_Intercuenca_49877/_raw_reportes_xlsx/IDConfig_65283_completo.xlsx
+++ b/49877_Intercuenca_49877/_raw_reportes_xlsx/IDConfig_65283_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re57a4a704ae049a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R41922232fefd447f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.0085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.4260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.5085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.4385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.4785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    165.2160</x:v>
+        <x:v>    164.9935</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49877_Intercuenca_49877/_raw_reportes_xlsx/IDConfig_65283_completo.xlsx
+++ b/49877_Intercuenca_49877/_raw_reportes_xlsx/IDConfig_65283_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R41922232fefd447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R414f7452b6e24f80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.7960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.7710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.3385</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.5785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.7785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3260</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.7910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.0035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3285</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.4160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.7860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.6585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    165.0335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    165.7460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    165.3835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.9310</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    165.2135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.7835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.5710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.0935</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8835</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.2635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.7910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.3035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.9785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.7585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    165.6435</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    165.7685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    164.6585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.8635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
